--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -5,28 +5,47 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation O360\YaminiCodeMaster\O360_Automation\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ArjunO360\O360-AI1\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF6B385-9FB8-42B0-B661-C0B39359E03A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27300DE8-4685-413D-BC4C-29F4FFC60570}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7245" tabRatio="784" firstSheet="5" activeTab="13" xr2:uid="{37B91979-A2CD-4275-8B46-28CAE73357A2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7245" tabRatio="784" firstSheet="28" activeTab="32" xr2:uid="{37B91979-A2CD-4275-8B46-28CAE73357A2}"/>
   </bookViews>
   <sheets>
-    <sheet name="EWCLeaveRequest_CompOffCredit" sheetId="27" r:id="rId1"/>
-    <sheet name="CandidateCreation" sheetId="13" r:id="rId2"/>
-    <sheet name="HrOnboardingPending" sheetId="15" r:id="rId3"/>
-    <sheet name="USEmailApproval" sheetId="14" r:id="rId4"/>
-    <sheet name="ConfirmPreboarding" sheetId="19" r:id="rId5"/>
-    <sheet name="ConfirmOnBoarding" sheetId="18" r:id="rId6"/>
-    <sheet name="TimeSheetModule" sheetId="20" r:id="rId7"/>
-    <sheet name="Timesheet_CancelRequests" sheetId="21" r:id="rId8"/>
-    <sheet name="Timesheet_Approvals" sheetId="22" r:id="rId9"/>
-    <sheet name="TimeSheeEditDelete" sheetId="23" r:id="rId10"/>
-    <sheet name="TimesheetOnBehalf" sheetId="24" r:id="rId11"/>
-    <sheet name="LeaveRequest" sheetId="25" r:id="rId12"/>
-    <sheet name="EWCLeaveRequest" sheetId="26" r:id="rId13"/>
-    <sheet name="ExpenseRequest" sheetId="28" r:id="rId14"/>
+    <sheet name="Employee_ApplicationTrcaker" sheetId="42" r:id="rId1"/>
+    <sheet name="EWCLeaveRequest_CompOffCredit" sheetId="27" r:id="rId2"/>
+    <sheet name="CandidateCreation" sheetId="13" r:id="rId3"/>
+    <sheet name="HrOnboardingPending" sheetId="15" r:id="rId4"/>
+    <sheet name="USEmailApproval" sheetId="14" r:id="rId5"/>
+    <sheet name="ConfirmPreboarding" sheetId="19" r:id="rId6"/>
+    <sheet name="ConfirmOnBoarding" sheetId="18" r:id="rId7"/>
+    <sheet name=" old" sheetId="20" r:id="rId8"/>
+    <sheet name="Timesheet_CancelRequests old" sheetId="21" r:id="rId9"/>
+    <sheet name="old timesheet" sheetId="22" r:id="rId10"/>
+    <sheet name="TimeSheeEditDelete old" sheetId="23" r:id="rId11"/>
+    <sheet name="TimesheetOnBehalf old" sheetId="24" r:id="rId12"/>
+    <sheet name="LeaveRequest" sheetId="25" r:id="rId13"/>
+    <sheet name="EWCLeaveRequest" sheetId="26" r:id="rId14"/>
+    <sheet name="ExpenseRequest" sheetId="28" r:id="rId15"/>
+    <sheet name="EmployeeDependantApproval" sheetId="29" r:id="rId16"/>
+    <sheet name="EmployeeDependantTab" sheetId="30" r:id="rId17"/>
+    <sheet name="ResignRequestApproval" sheetId="31" r:id="rId18"/>
+    <sheet name="EmpResignPage" sheetId="32" r:id="rId19"/>
+    <sheet name="EmpProfileReqApproval" sheetId="33" r:id="rId20"/>
+    <sheet name="EmpProfileTabEditing" sheetId="34" r:id="rId21"/>
+    <sheet name="ProjectModule" sheetId="35" r:id="rId22"/>
+    <sheet name="HR_Initiated_Transfer" sheetId="36" r:id="rId23"/>
+    <sheet name="Employee_Initiated_Transfer" sheetId="37" r:id="rId24"/>
+    <sheet name="Quick_Transfer_Reject" sheetId="38" r:id="rId25"/>
+    <sheet name="Transfer_Reject" sheetId="39" r:id="rId26"/>
+    <sheet name="Quick_Transfer_Approvals" sheetId="40" r:id="rId27"/>
+    <sheet name="Transfer_Approvals" sheetId="41" r:id="rId28"/>
+    <sheet name="TimeSheetModule" sheetId="43" r:id="rId29"/>
+    <sheet name="Timesheet_CancelRequests" sheetId="44" r:id="rId30"/>
+    <sheet name="Timesheet_Approvals" sheetId="45" r:id="rId31"/>
+    <sheet name="TimeSheeEditDelete" sheetId="46" r:id="rId32"/>
+    <sheet name="TimesheetOnBehalf" sheetId="47" r:id="rId33"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="361">
   <si>
     <t>Run</t>
   </si>
@@ -668,13 +687,466 @@
   </si>
   <si>
     <t>EXPSPIND837</t>
+  </si>
+  <si>
+    <t>LoginName</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>EmployeeUN</t>
+  </si>
+  <si>
+    <t>ApproveRelation</t>
+  </si>
+  <si>
+    <t>RejectRelation</t>
+  </si>
+  <si>
+    <t>TC_EmployeeDependantApproval</t>
+  </si>
+  <si>
+    <t>viswanathan.easwaran1</t>
+  </si>
+  <si>
+    <t>Donot Chnage Super user</t>
+  </si>
+  <si>
+    <t>SP10772</t>
+  </si>
+  <si>
+    <t>Donotmodify.Super</t>
+  </si>
+  <si>
+    <t>Spouse</t>
+  </si>
+  <si>
+    <t>Son</t>
+  </si>
+  <si>
+    <t>ApprovalName</t>
+  </si>
+  <si>
+    <t>TC_EmployeeDependantTab</t>
+  </si>
+  <si>
+    <t>Reshma.Murali</t>
+  </si>
+  <si>
+    <t>Reshma Murali</t>
+  </si>
+  <si>
+    <t>SP2486</t>
+  </si>
+  <si>
+    <t>FullName</t>
+  </si>
+  <si>
+    <t>SuperUser</t>
+  </si>
+  <si>
+    <t>TC_EmployeeResignApproval</t>
+  </si>
+  <si>
+    <t>Donot.Modify02</t>
+  </si>
+  <si>
+    <t>Donot Modify 02</t>
+  </si>
+  <si>
+    <t>SPC10763</t>
+  </si>
+  <si>
+    <t>donotmodify.super</t>
+  </si>
+  <si>
+    <t>KeyboardDate</t>
+  </si>
+  <si>
+    <t>InvalidDateWithDay</t>
+  </si>
+  <si>
+    <t>InvalidDatewithYear</t>
+  </si>
+  <si>
+    <t>SearchKeyword</t>
+  </si>
+  <si>
+    <t>InvalidKeywordSearch</t>
+  </si>
+  <si>
+    <t>LowerCase</t>
+  </si>
+  <si>
+    <t>UpperCase</t>
+  </si>
+  <si>
+    <t>FullNameOfEmp</t>
+  </si>
+  <si>
+    <t>TC_EmployeeResignCreation</t>
+  </si>
+  <si>
+    <t>26/11/2024</t>
+  </si>
+  <si>
+    <t>2025/11/34</t>
+  </si>
+  <si>
+    <t>Pay</t>
+  </si>
+  <si>
+    <t>Death</t>
+  </si>
+  <si>
+    <t>type of work</t>
+  </si>
+  <si>
+    <t>TYPE OF WORK</t>
+  </si>
+  <si>
+    <t>UserName1</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>EmpName</t>
+  </si>
+  <si>
+    <t>EmpName1</t>
+  </si>
+  <si>
+    <t>TC_Employee Profile Req Approval</t>
+  </si>
+  <si>
+    <t>Reject</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>PermaHouseNo</t>
+  </si>
+  <si>
+    <t>PermaHouseName</t>
+  </si>
+  <si>
+    <t>PermaStreet</t>
+  </si>
+  <si>
+    <t>PermaArea</t>
+  </si>
+  <si>
+    <t>PermaCity</t>
+  </si>
+  <si>
+    <t>PermaState</t>
+  </si>
+  <si>
+    <t>PermaZip</t>
+  </si>
+  <si>
+    <t>FatherName</t>
+  </si>
+  <si>
+    <t>MotherName</t>
+  </si>
+  <si>
+    <t>ContactPersonName</t>
+  </si>
+  <si>
+    <t>ContactPersonNumber</t>
+  </si>
+  <si>
+    <t>TC_Employee Profile Tab Editing</t>
+  </si>
+  <si>
+    <t>ahammed.thameem</t>
+  </si>
+  <si>
+    <t>Thameem Ahammed</t>
+  </si>
+  <si>
+    <t>Silver Edge 33</t>
+  </si>
+  <si>
+    <t>Kalamandir</t>
+  </si>
+  <si>
+    <t>Geeta Bhawan gate 2</t>
+  </si>
+  <si>
+    <t>INDORE</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>Vinay</t>
+  </si>
+  <si>
+    <t>Neha</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Projectname</t>
+  </si>
+  <si>
+    <t>Clientname</t>
+  </si>
+  <si>
+    <t>rdate</t>
+  </si>
+  <si>
+    <t>TC_ProjectModule</t>
+  </si>
+  <si>
+    <t>clement.joseph</t>
+  </si>
+  <si>
+    <t>Projectnewthree</t>
+  </si>
+  <si>
+    <t>clientnewone</t>
+  </si>
+  <si>
+    <t>DateOfTransfer</t>
+  </si>
+  <si>
+    <t>NewReportingTo</t>
+  </si>
+  <si>
+    <t>TransferType</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>NEWBUSINESSUNIT</t>
+  </si>
+  <si>
+    <t>NEWOFFICE</t>
+  </si>
+  <si>
+    <t>Fareen Jai</t>
+  </si>
+  <si>
+    <t>TC_HR_Initiated_Transfer</t>
+  </si>
+  <si>
+    <t>Aana C</t>
+  </si>
+  <si>
+    <t>Company Initiated Transfer</t>
+  </si>
+  <si>
+    <t>Ravikiran.Vallepu</t>
+  </si>
+  <si>
+    <t>Irvine - Speridian</t>
+  </si>
+  <si>
+    <t>EMPOFFICE</t>
+  </si>
+  <si>
+    <t>TC_Employee_Initiated_Transfer</t>
+  </si>
+  <si>
+    <t>hari.yadav1</t>
+  </si>
+  <si>
+    <t>Delhi NCR - Speridian</t>
+  </si>
+  <si>
+    <t>ApproverComments</t>
+  </si>
+  <si>
+    <t>EMPCODE</t>
+  </si>
+  <si>
+    <t>TC_Quick_Transfer_Reject</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>SP4118</t>
+  </si>
+  <si>
+    <t>TC_Transfer_Reject</t>
+  </si>
+  <si>
+    <t>SP3736</t>
+  </si>
+  <si>
+    <t>TC_Quick_Transfer_Approvals</t>
+  </si>
+  <si>
+    <t>SP3950</t>
+  </si>
+  <si>
+    <t>TC_Transfer_Approvals</t>
+  </si>
+  <si>
+    <t>SP10097</t>
+  </si>
+  <si>
+    <t>HiringClassification</t>
+  </si>
+  <si>
+    <t>Salutation</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>MiddleName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>PersonalEmail</t>
+  </si>
+  <si>
+    <t>ContactNumber</t>
+  </si>
+  <si>
+    <t>ReportingTo</t>
+  </si>
+  <si>
+    <t>RoleName</t>
+  </si>
+  <si>
+    <t>BusinessUnit</t>
+  </si>
+  <si>
+    <t>ImmigrationStatus</t>
+  </si>
+  <si>
+    <t>VisaType</t>
+  </si>
+  <si>
+    <t>DateOfJoining</t>
+  </si>
+  <si>
+    <t>EmploymentType</t>
+  </si>
+  <si>
+    <t>SpecialAccessNeeded</t>
+  </si>
+  <si>
+    <t>TrainingRequired</t>
+  </si>
+  <si>
+    <t>AdditionalTraining</t>
+  </si>
+  <si>
+    <t>JobLocation</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>ZipCode</t>
+  </si>
+  <si>
+    <t>SalaryType</t>
+  </si>
+  <si>
+    <t>AdditionalComments</t>
+  </si>
+  <si>
+    <t>TC_Employee_ApplicationTracker</t>
+  </si>
+  <si>
+    <t>Campus</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>Sony</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Mony</t>
+  </si>
+  <si>
+    <t>symy226.sm@yopmail.com</t>
+  </si>
+  <si>
+    <t>A Aare</t>
+  </si>
+  <si>
+    <t>.Net Developer</t>
+  </si>
+  <si>
+    <t>Architect</t>
+  </si>
+  <si>
+    <t>Benefitalign India</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Analytics</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>01-15-2025</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Banglore</t>
+  </si>
+  <si>
+    <t>Karnataka</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
+  <si>
+    <t>Per Hour</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>May 18 - May 24</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 </t>
+  </si>
+  <si>
+    <t>Swiss solutions inc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -693,6 +1165,61 @@
     <font>
       <sz val="9"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A00FF"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -759,10 +1286,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -818,8 +1346,77 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1131,187 +1728,317 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58A15975-1EF1-4541-8083-A56DE49427DB}">
-  <dimension ref="A1:AA2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08530B9C-4267-4988-BE10-30D04D9192FB}">
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.5703125" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.7109375" customWidth="1"/>
-    <col min="23" max="23" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="28.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" customWidth="1"/>
+    <col min="17" max="17" width="17.140625" customWidth="1"/>
+    <col min="19" max="19" width="13.85546875" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.28515625" customWidth="1"/>
+    <col min="22" max="22" width="17.5703125" customWidth="1"/>
+    <col min="23" max="23" width="19.5703125" customWidth="1"/>
+    <col min="24" max="24" width="14" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" customWidth="1"/>
+    <col min="31" max="31" width="12.5703125" customWidth="1"/>
+    <col min="32" max="32" width="21.5703125" customWidth="1"/>
+    <col min="33" max="33" width="18.5703125" customWidth="1"/>
+    <col min="34" max="34" width="18" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" customWidth="1"/>
+    <col min="36" max="36" width="15" customWidth="1"/>
+    <col min="37" max="37" width="18.28515625" customWidth="1"/>
+    <col min="38" max="38" width="27.85546875" customWidth="1"/>
+    <col min="39" max="39" width="11.7109375" customWidth="1"/>
+    <col min="40" max="40" width="19.7109375" customWidth="1"/>
+    <col min="41" max="41" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="S1" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="U1" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="V1" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="W1" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="X1" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y1" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z1" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA1" s="10" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="50" t="s">
+        <v>312</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="F1" s="50" t="s">
+        <v>315</v>
+      </c>
+      <c r="G1" s="50" t="s">
+        <v>316</v>
+      </c>
+      <c r="H1" s="50" t="s">
+        <v>317</v>
+      </c>
+      <c r="I1" s="50" t="s">
+        <v>318</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="M1" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="N1" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="R1" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="S1" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="T1" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="U1" s="50" t="s">
+        <v>326</v>
+      </c>
+      <c r="V1" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="W1" s="50" t="s">
+        <v>328</v>
+      </c>
+      <c r="X1" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="Y1" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="Z1" s="50" t="s">
+        <v>331</v>
+      </c>
+      <c r="AA1" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB1" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC1" s="50" t="s">
+        <v>185</v>
+      </c>
+      <c r="AD1" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE1" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="AF1" s="50" t="s">
+        <v>333</v>
+      </c>
+      <c r="AG1" s="50" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>168</v>
+        <v>334</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D2" s="14">
-        <v>2025</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="F2" s="23">
-        <v>9</v>
-      </c>
-      <c r="G2" s="14">
-        <v>2025</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="I2" s="23">
-        <v>9</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="L2" s="14" t="s">
+      <c r="C2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G2" t="s">
+        <v>339</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>340</v>
+      </c>
+      <c r="I2">
+        <v>9889405395</v>
+      </c>
+      <c r="J2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L2" t="s">
+        <v>343</v>
+      </c>
+      <c r="M2" t="s">
+        <v>344</v>
+      </c>
+      <c r="N2" t="s">
+        <v>345</v>
+      </c>
+      <c r="O2" t="s">
+        <v>346</v>
+      </c>
+      <c r="P2" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" t="s">
+        <v>348</v>
+      </c>
+      <c r="S2" s="49" t="s">
+        <v>349</v>
+      </c>
+      <c r="T2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U2" t="s">
+        <v>2</v>
+      </c>
+      <c r="V2" t="s">
+        <v>2</v>
+      </c>
+      <c r="W2" t="s">
+        <v>2</v>
+      </c>
+      <c r="X2" t="s">
+        <v>350</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>351</v>
+      </c>
+      <c r="Z2">
+        <v>90001</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>352</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>353</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>354</v>
+      </c>
+      <c r="AD2">
+        <v>100000</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>355</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{0F15AA83-BB5A-4AC8-B4C6-1859D69B0A5D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26AF835-F3DC-4258-B7E9-8A704E59D479}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="21.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H2" s="18"/>
+      <c r="I2" s="19" t="s">
         <v>125</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="P2" s="14">
-        <v>2025</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="R2" s="23">
-        <v>15</v>
-      </c>
-      <c r="S2" s="14">
-        <v>2025</v>
-      </c>
-      <c r="T2" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="U2" s="23">
-        <v>15</v>
-      </c>
-      <c r="V2" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="W2" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="X2" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y2" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z2" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA2" s="15" t="s">
-        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -1319,7 +2046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640F365E-94FE-4AC2-B5FD-37792E4BEBBE}">
   <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultColWidth="24.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1453,7 +2180,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C20F9C3-2077-46DF-BDF9-91D3A9296BF6}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1510,7 +2237,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26032F91-1D32-41C8-80B5-14F121CB54B9}">
   <dimension ref="A1:AR4"/>
   <sheetFormatPr defaultColWidth="24.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1683,7 +2410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEB7CED6-2F35-4F60-8CB2-DEC660DA37B0}">
   <dimension ref="A1:AR6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1913,7 +2640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C2F894F-4DFC-4FBB-B719-9794E831E694}">
   <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2110,7 +2837,1313 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214CB241-6E87-4836-A252-56ABB1392CCF}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C35003D-32FF-4C4E-B8D9-01131ECA7595}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="14.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>226</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{295F87F1-5A5B-4876-8D59-558CC8D6B386}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="12.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079E8DE2-777B-41A3-A3B2-D3A654D4814A}">
+  <dimension ref="A1:W2"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" style="37" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="12.42578125" style="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A2" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="35">
+        <v>45819</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58A15975-1EF1-4541-8083-A56DE49427DB}">
+  <dimension ref="A1:AA2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5703125" customWidth="1"/>
+    <col min="15" max="15" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" customWidth="1"/>
+    <col min="23" max="23" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="V1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="X1" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y1" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA1" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" s="14">
+        <v>2025</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" s="23">
+        <v>9</v>
+      </c>
+      <c r="G2" s="14">
+        <v>2025</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="I2" s="23">
+        <v>9</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="P2" s="14">
+        <v>2025</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="R2" s="23">
+        <v>15</v>
+      </c>
+      <c r="S2" s="14">
+        <v>2025</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="U2" s="23">
+        <v>15</v>
+      </c>
+      <c r="V2" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="W2" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="X2" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y2" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z2" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA2" s="15" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C9AFBD-E4D6-4804-9B2B-3F6869F8ABB2}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>231</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{001E4462-9A8A-44AF-8790-6421B6761FA3}">
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr defaultColWidth="47.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="48" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" style="48" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="48" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" style="48" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.5703125" style="48" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="47.140625" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" s="41" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+    </row>
+    <row r="2" spans="1:21" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>269</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2" s="42">
+        <v>207</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="K2" s="45" t="s">
+        <v>274</v>
+      </c>
+      <c r="L2" s="45">
+        <v>678901</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="N2" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="O2" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="P2" s="23">
+        <v>8989786545</v>
+      </c>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28F220E-131D-4310-9F23-98983252B9E2}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F2" s="49">
+        <v>46110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1AA0AA-5B10-429D-A29E-0FC5EF10B185}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.28515625" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="F1" s="50" t="s">
+        <v>287</v>
+      </c>
+      <c r="G1" s="50" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1" s="50" t="s">
+        <v>255</v>
+      </c>
+      <c r="I1" s="50" t="s">
+        <v>289</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="49">
+        <v>45964</v>
+      </c>
+      <c r="E2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>295</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62344A48-69E5-43B8-9D14-1FAC502B49A4}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>288</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>255</v>
+      </c>
+      <c r="F1" s="50" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="49">
+        <v>45841</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9FF69B3-FB8A-4104-AD10-C989AE02930E}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA470D58-E3E5-4753-9210-1D5B01DBCD6E}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3798E0BB-1226-41F0-BA00-FA57325FB1DF}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E40C18C-8A6A-4622-AC55-0F628036286B}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152573A1-17E3-4203-AC06-D8BFD7C45051}">
+  <dimension ref="A1:AO2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.5703125" customWidth="1"/>
+    <col min="3" max="4" width="40.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.5703125" customWidth="1"/>
+    <col min="13" max="13" width="21" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="27.42578125" customWidth="1"/>
+    <col min="19" max="19" width="27.85546875" customWidth="1"/>
+    <col min="20" max="20" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.7109375" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" customWidth="1"/>
+    <col min="27" max="27" width="14" customWidth="1"/>
+    <col min="40" max="40" width="21.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="V1" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="10"/>
+      <c r="AH1" s="10"/>
+      <c r="AI1" s="10"/>
+      <c r="AJ1" s="10"/>
+      <c r="AK1" s="10"/>
+      <c r="AL1" s="10"/>
+      <c r="AM1" s="10"/>
+      <c r="AN1" s="12"/>
+      <c r="AO1" s="12"/>
+    </row>
+    <row r="2" spans="1:41" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" s="15">
+        <v>8</v>
+      </c>
+      <c r="I2" s="14">
+        <v>0</v>
+      </c>
+      <c r="J2" s="14">
+        <v>19</v>
+      </c>
+      <c r="K2" s="14">
+        <v>26</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q2" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="R2" s="14">
+        <v>1</v>
+      </c>
+      <c r="S2" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="V2" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4CBCCBB-F620-4A1E-BF48-EA55E11F2AC6}">
   <dimension ref="A1:AM2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2391,7 +4424,367 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85ADAB9A-D995-469E-ADFD-83DA6A62D49E}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="27.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H2" s="18"/>
+      <c r="I2" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="J2" s="52" t="s">
+        <v>282</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FC31E0-B694-46DC-97A1-9877EF138762}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultColWidth="21.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H2" s="18"/>
+      <c r="I2" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="J2" s="52" t="s">
+        <v>282</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5BF7F1-B735-432B-91CB-B3923E058B7F}">
+  <dimension ref="A1:AO2"/>
+  <sheetFormatPr defaultColWidth="24.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="10"/>
+      <c r="AH1" s="10"/>
+      <c r="AI1" s="10"/>
+      <c r="AJ1" s="10"/>
+      <c r="AK1" s="10"/>
+      <c r="AL1" s="10"/>
+      <c r="AM1" s="10"/>
+      <c r="AN1" s="12"/>
+      <c r="AO1" s="12"/>
+    </row>
+    <row r="2" spans="1:41" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="15">
+        <v>6</v>
+      </c>
+      <c r="H2" s="14">
+        <v>30</v>
+      </c>
+      <c r="I2" s="14">
+        <v>14</v>
+      </c>
+      <c r="J2" s="14">
+        <v>15</v>
+      </c>
+      <c r="K2" s="52" t="s">
+        <v>282</v>
+      </c>
+      <c r="L2" s="15"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9311BC-7647-48BC-960A-A6428A48C8D5}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2" s="52" t="s">
+        <v>282</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A94568-BE7D-4A57-AE37-C45034A52044}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2434,7 +4827,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFDCC8D-039F-437D-A845-22D1EF423E12}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2487,7 +4880,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70ED1544-2BE3-4FC2-826F-03DF821EF92D}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2530,7 +4923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6B0AE9-A7B4-47F8-8613-52E7DBD9E269}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2566,7 +4959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD0D49B-4275-4C29-A7E4-3E5D2E2F9AC6}">
   <dimension ref="A1:AN2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2775,7 +5168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98277668-9C38-45A0-81A5-4103268AE99B}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2850,73 +5243,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26AF835-F3DC-4258-B7E9-8A704E59D479}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="21.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="32.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19" t="s">
-        <v>125</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ArjunO360\O360-AI1\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajesh.ganesh\OneDrive - Speridian Technologies\Desktop\Automation\O360-AI1\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F552B83-7D55-4E60-AA6E-CF163A57A813}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7245" tabRatio="784" xr2:uid="{37B91979-A2CD-4275-8B46-28CAE73357A2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7245" tabRatio="784" firstSheet="35" activeTab="40"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="54" r:id="rId1"/>
@@ -53,8 +52,9 @@
     <sheet name="Timesheet_Approvals" sheetId="45" r:id="rId38"/>
     <sheet name="TimeSheeEditDelete" sheetId="46" r:id="rId39"/>
     <sheet name="TimesheetOnBehalf" sheetId="47" r:id="rId40"/>
+    <sheet name="TimeSheetNew" sheetId="55" r:id="rId41"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="447">
   <si>
     <t>Run</t>
   </si>
@@ -1137,18 +1137,6 @@
     <t>May</t>
   </si>
   <si>
-    <t>May 18 - May 24</t>
-  </si>
-  <si>
-    <t>Sep</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1 </t>
-  </si>
-  <si>
-    <t>Swiss solutions inc</t>
-  </si>
-  <si>
     <t>Subject</t>
   </si>
   <si>
@@ -1381,12 +1369,48 @@
   </si>
   <si>
     <t>SPIND/O360/5089</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MAY 18 - MAY 24 </t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>range</t>
+  </si>
+  <si>
+    <t>Deployment/ Prod Cutover</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> June </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JUN 01 - JUN 07 </t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>Mario.Noronha</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>O360@uaL!tY2O2twO</t>
+  </si>
+  <si>
+    <t>empName</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1531,7 +1555,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1663,6 +1687,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1977,7 +2003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3618E37C-E82D-41F4-A0F6-14F2CE1C7F19}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1986,7 +2012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4CBCCBB-F620-4A1E-BF48-EA55E11F2AC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AM2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2267,7 +2293,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A94568-BE7D-4A57-AE37-C45034A52044}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2310,7 +2336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFDCC8D-039F-437D-A845-22D1EF423E12}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2356,14 +2382,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{8EFBC8F0-A848-41E5-BE64-C210D89A31CA}"/>
+    <hyperlink ref="D2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70ED1544-2BE3-4FC2-826F-03DF821EF92D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2406,7 +2432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6B0AE9-A7B4-47F8-8613-52E7DBD9E269}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2442,7 +2468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD0D49B-4275-4C29-A7E4-3E5D2E2F9AC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AN2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2651,7 +2677,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98277668-9C38-45A0-81A5-4103268AE99B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2728,7 +2754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26AF835-F3DC-4258-B7E9-8A704E59D479}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="21.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2797,7 +2823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640F365E-94FE-4AC2-B5FD-37792E4BEBBE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultColWidth="24.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2931,7 +2957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C20F9C3-2077-46DF-BDF9-91D3A9296BF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2988,7 +3014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C05CB830-F643-4561-AC36-C2A46C3A1D52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3015,62 +3041,62 @@
         <v>277</v>
       </c>
       <c r="D1" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="H1" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>366</v>
-      </c>
       <c r="J1" s="12" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="J2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -3080,7 +3106,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26032F91-1D32-41C8-80B5-14F121CB54B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AR4"/>
   <sheetFormatPr defaultColWidth="24.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3253,7 +3279,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEB7CED6-2F35-4F60-8CB2-DEC660DA37B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AR6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3483,7 +3509,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C2F894F-4DFC-4FBB-B719-9794E831E694}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3680,7 +3706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214CB241-6E87-4836-A252-56ABB1392CCF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3753,7 +3779,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C35003D-32FF-4C4E-B8D9-01131ECA7595}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="14.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3812,7 +3838,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{295F87F1-5A5B-4876-8D59-558CC8D6B386}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="12.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3870,7 +3896,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079E8DE2-777B-41A3-A3B2-D3A654D4814A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3992,7 +4018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C9AFBD-E4D6-4804-9B2B-3F6869F8ABB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4058,7 +4084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{001E4462-9A8A-44AF-8790-6421B6761FA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="47.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4196,7 +4222,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28F220E-131D-4310-9F23-98983252B9E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4253,7 +4279,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B18F116-67D9-4FE1-A623-E49CFCDC1863}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4273,38 +4299,38 @@
         <v>277</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C3" s="13" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -4313,7 +4339,7 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1AA0AA-5B10-429D-A29E-0FC5EF10B185}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4398,7 +4424,7 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62344A48-69E5-43B8-9D14-1FAC502B49A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4456,7 +4482,7 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9FF69B3-FB8A-4104-AD10-C989AE02930E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4504,7 +4530,7 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA470D58-E3E5-4753-9210-1D5B01DBCD6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4553,7 +4579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3798E0BB-1226-41F0-BA00-FA57325FB1DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4601,7 +4627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E40C18C-8A6A-4622-AC55-0F628036286B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4652,7 +4678,7 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152573A1-17E3-4203-AC06-D8BFD7C45051}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4665,7 +4691,7 @@
     <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.5703125" customWidth="1"/>
-    <col min="13" max="13" width="21" customWidth="1"/>
+    <col min="13" max="13" width="21" style="58" customWidth="1"/>
     <col min="14" max="14" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="28" customWidth="1"/>
     <col min="16" max="16" width="20.7109375" customWidth="1"/>
@@ -4716,7 +4742,7 @@
       <c r="L1" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="57" t="s">
         <v>92</v>
       </c>
       <c r="N1" s="10" t="s">
@@ -4803,8 +4829,8 @@
       <c r="L2" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>357</v>
+      <c r="M2" s="8" t="s">
+        <v>435</v>
       </c>
       <c r="N2" s="14" t="s">
         <v>111</v>
@@ -4813,16 +4839,16 @@
         <v>105</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="Q2" s="16" t="s">
-        <v>359</v>
+        <v>356</v>
+      </c>
+      <c r="Q2" s="15">
+        <v>18</v>
       </c>
       <c r="R2" s="14">
         <v>1</v>
       </c>
-      <c r="S2" s="14" t="s">
-        <v>114</v>
+      <c r="S2" s="13" t="s">
+        <v>105</v>
       </c>
       <c r="T2" s="6" t="s">
         <v>115</v>
@@ -4830,8 +4856,8 @@
       <c r="U2" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="V2" s="14" t="s">
-        <v>360</v>
+      <c r="V2" s="13" t="s">
+        <v>105</v>
       </c>
       <c r="W2" s="17"/>
       <c r="X2" s="17"/>
@@ -4857,7 +4883,7 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85ADAB9A-D995-469E-ADFD-83DA6A62D49E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4912,7 +4938,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>118</v>
@@ -4941,7 +4967,7 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FC31E0-B694-46DC-97A1-9877EF138762}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="21.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5016,7 +5042,7 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5BF7F1-B735-432B-91CB-B3923E058B7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultColWidth="24.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5093,7 +5119,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>128</v>
@@ -5111,10 +5137,10 @@
         <v>30</v>
       </c>
       <c r="I2" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J2" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K2" s="52" t="s">
         <v>282</v>
@@ -5154,7 +5180,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D4DEE5-F39A-47A7-911C-C765D6D534B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5182,80 +5208,80 @@
         <v>122</v>
       </c>
       <c r="E1" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="K1" s="10" t="s">
-        <v>370</v>
-      </c>
       <c r="L1" s="10" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="D2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="D2" t="s">
+      <c r="M2" t="s">
         <v>426</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>427</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>410</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="M2" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D3" s="6" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -5264,7 +5290,7 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9311BC-7647-48BC-960A-A6428A48C8D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5326,8 +5352,118 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.85546875" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="23.42578125" customWidth="1"/>
+    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" customWidth="1"/>
+    <col min="11" max="11" width="5.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+    </row>
+    <row r="2" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="I2" s="14">
+        <v>2025</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="K2" s="14">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="M2" s="15"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="52"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{648EA32A-7D96-47D7-90E7-95212629AF91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5352,106 +5488,106 @@
         <v>277</v>
       </c>
       <c r="D1" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="R1" s="10" t="s">
         <v>362</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="J2" s="14"/>
       <c r="K2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="14" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="N2" s="23" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="O2" s="14" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="P2" s="14" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="Q2" s="23" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -5461,7 +5597,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD8E4AC-A0D3-40DE-9448-FC9C9D66CEFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5494,125 +5630,125 @@
         <v>277</v>
       </c>
       <c r="D1" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="U1" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="S1" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="U1" s="10" t="s">
-        <v>366</v>
-      </c>
       <c r="V1" s="10" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="J2" s="23"/>
       <c r="K2" s="6"/>
       <c r="L2" s="5" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="M2" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="N2" t="s">
+        <v>404</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q2" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="R2" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="N2" t="s">
+      <c r="S2" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="T2" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="U2" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="O2" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="P2" s="21" t="s">
+      <c r="V2" s="56" t="s">
         <v>409</v>
-      </c>
-      <c r="Q2" s="23" t="s">
-        <v>410</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="T2" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="U2" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="V2" s="56" t="s">
-        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -5622,7 +5758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A3AE85-FBFB-494B-AD4C-727F1C9B62D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5657,129 +5793,129 @@
         <v>277</v>
       </c>
       <c r="D1" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="E1" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="F1" s="54" t="s">
+        <v>359</v>
+      </c>
+      <c r="G1" s="54" t="s">
+        <v>360</v>
+      </c>
+      <c r="H1" s="54" t="s">
         <v>361</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="I1" s="54" t="s">
         <v>362</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="J1" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="K1" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="L1" s="54" t="s">
         <v>365</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="M1" s="54" t="s">
         <v>366</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="N1" s="54" t="s">
         <v>367</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="O1" s="54" t="s">
         <v>368</v>
       </c>
-      <c r="L1" s="54" t="s">
+      <c r="P1" s="54" t="s">
         <v>369</v>
       </c>
-      <c r="M1" s="54" t="s">
+      <c r="Q1" s="54" t="s">
         <v>370</v>
       </c>
-      <c r="N1" s="54" t="s">
+      <c r="R1" s="54" t="s">
         <v>371</v>
       </c>
-      <c r="O1" s="54" t="s">
+      <c r="S1" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="P1" s="54" t="s">
+      <c r="T1" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="Q1" s="54" t="s">
+      <c r="U1" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="R1" s="54" t="s">
+      <c r="V1" s="10" t="s">
         <v>375</v>
-      </c>
-      <c r="S1" s="54" t="s">
-        <v>376</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="U1" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="V1" s="10" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>381</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="H2" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="I2" s="23" t="s">
         <v>383</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="J2" s="23" t="s">
         <v>384</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="K2" t="s">
         <v>385</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="L2" s="23" t="s">
         <v>386</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="M2" s="23" t="s">
         <v>387</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="N2" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="K2" t="s">
+      <c r="O2" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="P2" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="Q2" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="R2" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="S2" s="21" t="s">
         <v>393</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="T2" s="23" t="s">
         <v>394</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>395</v>
-      </c>
-      <c r="R2" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="S2" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="T2" s="23" t="s">
-        <v>398</v>
       </c>
       <c r="U2" s="5">
         <v>1</v>
       </c>
       <c r="V2" s="55" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -5789,7 +5925,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08530B9C-4267-4988-BE10-30D04D9192FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6031,7 +6167,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{0F15AA83-BB5A-4AC8-B4C6-1859D69B0A5D}"/>
+    <hyperlink ref="H2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -6039,7 +6175,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58A15975-1EF1-4541-8083-A56DE49427DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7245" tabRatio="784" firstSheet="35" activeTab="40"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7245" tabRatio="784" firstSheet="36" activeTab="41"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="54" r:id="rId1"/>
@@ -53,6 +53,7 @@
     <sheet name="TimeSheeEditDelete" sheetId="46" r:id="rId39"/>
     <sheet name="TimesheetOnBehalf" sheetId="47" r:id="rId40"/>
     <sheet name="TimeSheetNew" sheetId="55" r:id="rId41"/>
+    <sheet name="Expenses" sheetId="56" r:id="rId42"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="473">
   <si>
     <t>Run</t>
   </si>
@@ -1405,6 +1406,84 @@
   </si>
   <si>
     <t>empName</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>expenseType</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>JUN</t>
+  </si>
+  <si>
+    <t>Operational Expense:Accomodation Expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Only Reimbursable </t>
+  </si>
+  <si>
+    <t>firstLevel</t>
+  </si>
+  <si>
+    <t>SecondLevel</t>
+  </si>
+  <si>
+    <t>thirdLevel</t>
+  </si>
+  <si>
+    <t>Vivek.Nair</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Satish.Ganta</t>
+  </si>
+  <si>
+    <t>KP.Hari</t>
+  </si>
+  <si>
+    <t>sajitha.rahul</t>
+  </si>
+  <si>
+    <t>billVerificationStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bill Verification Completed </t>
+  </si>
+  <si>
+    <t>accountVerificationUserName</t>
+  </si>
+  <si>
+    <t>ratna.meenakshi</t>
+  </si>
+  <si>
+    <t>accVerificationPaymentStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Payroll Processed </t>
+  </si>
+  <si>
+    <t>accVerificationPaymentOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aug : 2025 </t>
+  </si>
+  <si>
+    <t>paymentStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Payment Done </t>
+  </si>
+  <si>
+    <t>billVerificationUserName</t>
   </si>
 </sst>
 </file>
@@ -1503,7 +1582,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1550,12 +1629,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1689,6 +1801,15 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5462,6 +5583,173 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" customWidth="1"/>
+    <col min="3" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" customWidth="1"/>
+    <col min="8" max="8" width="5.28515625" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="15.28515625" customWidth="1"/>
+    <col min="18" max="18" width="26.7109375" customWidth="1"/>
+    <col min="19" max="19" width="17" customWidth="1"/>
+    <col min="20" max="20" width="18.140625" customWidth="1"/>
+    <col min="21" max="21" width="10.85546875" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2025</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="H2" s="13">
+        <v>10</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>452</v>
+      </c>
+      <c r="L2" s="13">
+        <v>122</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="N2" s="59" t="s">
+        <v>457</v>
+      </c>
+      <c r="O2" s="61" t="s">
+        <v>459</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q2" s="60" t="s">
+        <v>461</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>471</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R3"/>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajesh.ganesh\OneDrive - Speridian Technologies\Desktop\Automation\O360-AI1\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Automation NEw\Arjun All Automation scripts\Rajesh 3\O360-AI1\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8DA5F7-D6CA-4777-BDAF-7315E4C71F5C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7245" tabRatio="784" firstSheet="36" activeTab="41"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7245" tabRatio="784" firstSheet="16" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="54" r:id="rId1"/>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="475">
   <si>
     <t>Run</t>
   </si>
@@ -1390,9 +1391,6 @@
     <t xml:space="preserve"> June </t>
   </si>
   <si>
-    <t xml:space="preserve"> JUN 01 - JUN 07 </t>
-  </si>
-  <si>
     <t>day</t>
   </si>
   <si>
@@ -1484,12 +1482,21 @@
   </si>
   <si>
     <t>billVerificationUserName</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JUN 08 - JUN 14 </t>
+  </si>
+  <si>
+    <t>TC_Expenses</t>
+  </si>
+  <si>
+    <t>JUL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2124,7 +2131,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2133,7 +2140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:AM2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2414,7 +2421,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2457,7 +2464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2503,14 +2510,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2553,7 +2560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2589,7 +2596,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:AN2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2798,7 +2805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2875,7 +2882,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="21.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2944,7 +2951,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultColWidth="24.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3078,7 +3085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3135,7 +3142,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3227,7 +3234,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:AR4"/>
   <sheetFormatPr defaultColWidth="24.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3319,19 +3326,19 @@
         <v>2025</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>150</v>
+        <v>474</v>
       </c>
       <c r="F2" s="22">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G2" s="14">
         <v>2025</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>150</v>
+        <v>474</v>
       </c>
       <c r="I2" s="23">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
         <v>151</v>
@@ -3400,7 +3407,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:AR6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3630,7 +3637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3827,7 +3834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3900,7 +3907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="14.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3959,7 +3966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="12.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4017,7 +4024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4139,7 +4146,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4205,7 +4212,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="47.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4343,7 +4350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4400,7 +4407,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4460,7 +4467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4545,7 +4552,7 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4603,7 +4610,7 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4651,7 +4658,7 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4700,7 +4707,7 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4748,7 +4755,7 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4799,7 +4806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5004,7 +5011,7 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5088,7 +5095,7 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="21.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5163,7 +5170,7 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultColWidth="24.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5301,7 +5308,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5411,7 +5418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5474,7 +5481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5502,13 +5509,13 @@
         <v>255</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>379</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>83</v>
@@ -5523,7 +5530,7 @@
         <v>437</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>438</v>
@@ -5548,10 +5555,10 @@
         <v>125</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>181</v>
@@ -5566,10 +5573,10 @@
         <v>440</v>
       </c>
       <c r="K2" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>441</v>
+        <v>472</v>
       </c>
       <c r="M2" s="15"/>
       <c r="N2" s="14"/>
@@ -5584,7 +5591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5620,10 +5627,10 @@
         <v>255</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>436</v>
@@ -5632,54 +5639,54 @@
         <v>437</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I1" s="10" t="s">
         <v>83</v>
       </c>
       <c r="J1" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="K1" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="M1" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="M1" s="10" t="s">
-        <v>450</v>
-      </c>
       <c r="N1" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="O1" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="P1" s="12" t="s">
         <v>455</v>
       </c>
-      <c r="P1" s="12" t="s">
-        <v>456</v>
-      </c>
       <c r="Q1" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="R1" s="12" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="T1" s="12" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="U1" s="12" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="V1" s="12" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:22" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>104</v>
+        <v>473</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
@@ -5688,7 +5695,7 @@
         <v>282</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>125</v>
@@ -5697,7 +5704,7 @@
         <v>2025</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H2" s="13">
         <v>10</v>
@@ -5709,40 +5716,40 @@
         <v>201</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L2" s="13">
         <v>122</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N2" s="59" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O2" s="61" t="s">
+        <v>458</v>
+      </c>
+      <c r="P2" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="Q2" s="60" t="s">
         <v>460</v>
       </c>
-      <c r="Q2" s="60" t="s">
-        <v>461</v>
-      </c>
       <c r="R2" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -5751,7 +5758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5885,7 +5892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6046,7 +6053,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6213,7 +6220,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6455,7 +6462,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -6463,7 +6470,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
